--- a/report_3.xlsx
+++ b/report_3.xlsx
@@ -9919,7 +9919,7 @@
         <v>41976</v>
       </c>
       <c r="E2" t="n">
-        <v>4154</v>
+        <v>4159</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -9945,7 +9945,7 @@
         <v>42046</v>
       </c>
       <c r="E3" t="n">
-        <v>4084</v>
+        <v>4089</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -9971,7 +9971,7 @@
         <v>42064</v>
       </c>
       <c r="E4" t="n">
-        <v>4066</v>
+        <v>4071</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -9997,7 +9997,7 @@
         <v>42167</v>
       </c>
       <c r="E5" t="n">
-        <v>3963</v>
+        <v>3968</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -10023,7 +10023,7 @@
         <v>42412</v>
       </c>
       <c r="E6" t="n">
-        <v>3718</v>
+        <v>3723</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -10049,7 +10049,7 @@
         <v>42493</v>
       </c>
       <c r="E7" t="n">
-        <v>3637</v>
+        <v>3642</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -10075,7 +10075,7 @@
         <v>42712</v>
       </c>
       <c r="E8" t="n">
-        <v>3418</v>
+        <v>3423</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -10101,7 +10101,7 @@
         <v>42897</v>
       </c>
       <c r="E9" t="n">
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -10127,7 +10127,7 @@
         <v>42925</v>
       </c>
       <c r="E10" t="n">
-        <v>3205</v>
+        <v>3210</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -10153,7 +10153,7 @@
         <v>42986</v>
       </c>
       <c r="E11" t="n">
-        <v>3144</v>
+        <v>3149</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -10179,7 +10179,7 @@
         <v>43161</v>
       </c>
       <c r="E12" t="n">
-        <v>2969</v>
+        <v>2974</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -10205,7 +10205,7 @@
         <v>43163</v>
       </c>
       <c r="E13" t="n">
-        <v>2967</v>
+        <v>2972</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -10231,7 +10231,7 @@
         <v>43291</v>
       </c>
       <c r="E14" t="n">
-        <v>2839</v>
+        <v>2844</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -10257,7 +10257,7 @@
         <v>43587</v>
       </c>
       <c r="E15" t="n">
-        <v>2543</v>
+        <v>2548</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -10283,7 +10283,7 @@
         <v>43656</v>
       </c>
       <c r="E16" t="n">
-        <v>2474</v>
+        <v>2479</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -10309,7 +10309,7 @@
         <v>43740</v>
       </c>
       <c r="E17" t="n">
-        <v>2390</v>
+        <v>2395</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -10335,7 +10335,7 @@
         <v>43778</v>
       </c>
       <c r="E18" t="n">
-        <v>2352</v>
+        <v>2357</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -10361,7 +10361,7 @@
         <v>43837</v>
       </c>
       <c r="E19" t="n">
-        <v>2293</v>
+        <v>2298</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -10387,7 +10387,7 @@
         <v>43871</v>
       </c>
       <c r="E20" t="n">
-        <v>2259</v>
+        <v>2264</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -10413,7 +10413,7 @@
         <v>43898</v>
       </c>
       <c r="E21" t="n">
-        <v>2232</v>
+        <v>2237</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -10439,7 +10439,7 @@
         <v>43993</v>
       </c>
       <c r="E22" t="n">
-        <v>2137</v>
+        <v>2142</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -10465,7 +10465,7 @@
         <v>44015</v>
       </c>
       <c r="E23" t="n">
-        <v>2115</v>
+        <v>2120</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -10491,7 +10491,7 @@
         <v>44075</v>
       </c>
       <c r="E24" t="n">
-        <v>2055</v>
+        <v>2060</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -10517,7 +10517,7 @@
         <v>44083</v>
       </c>
       <c r="E25" t="n">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -10543,7 +10543,7 @@
         <v>44083</v>
       </c>
       <c r="E26" t="n">
-        <v>2047</v>
+        <v>2052</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -10569,7 +10569,7 @@
         <v>44109</v>
       </c>
       <c r="E27" t="n">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -10595,7 +10595,7 @@
         <v>44113</v>
       </c>
       <c r="E28" t="n">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -10621,7 +10621,7 @@
         <v>44177</v>
       </c>
       <c r="E29" t="n">
-        <v>1953</v>
+        <v>1958</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -10647,7 +10647,7 @@
         <v>44259</v>
       </c>
       <c r="E30" t="n">
-        <v>1871</v>
+        <v>1876</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -10673,7 +10673,7 @@
         <v>44383</v>
       </c>
       <c r="E31" t="n">
-        <v>1747</v>
+        <v>1752</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -10699,7 +10699,7 @@
         <v>44564</v>
       </c>
       <c r="E32" t="n">
-        <v>1566</v>
+        <v>1571</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -10725,7 +10725,7 @@
         <v>44566</v>
       </c>
       <c r="E33" t="n">
-        <v>1564</v>
+        <v>1569</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -10751,7 +10751,7 @@
         <v>44599</v>
       </c>
       <c r="E34" t="n">
-        <v>1531</v>
+        <v>1536</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -10777,7 +10777,7 @@
         <v>44659</v>
       </c>
       <c r="E35" t="n">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -10803,7 +10803,7 @@
         <v>44684</v>
       </c>
       <c r="E36" t="n">
-        <v>1446</v>
+        <v>1451</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         <v>44719</v>
       </c>
       <c r="E37" t="n">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -10855,7 +10855,7 @@
         <v>44753</v>
       </c>
       <c r="E38" t="n">
-        <v>1377</v>
+        <v>1382</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -10881,7 +10881,7 @@
         <v>44777</v>
       </c>
       <c r="E39" t="n">
-        <v>1353</v>
+        <v>1358</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -10907,7 +10907,7 @@
         <v>44785</v>
       </c>
       <c r="E40" t="n">
-        <v>1345</v>
+        <v>1350</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -10933,7 +10933,7 @@
         <v>44842</v>
       </c>
       <c r="E41" t="n">
-        <v>1288</v>
+        <v>1293</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -10959,7 +10959,7 @@
         <v>44961</v>
       </c>
       <c r="E42" t="n">
-        <v>1169</v>
+        <v>1174</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -10985,7 +10985,7 @@
         <v>44968</v>
       </c>
       <c r="E43" t="n">
-        <v>1162</v>
+        <v>1167</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -11011,7 +11011,7 @@
         <v>44993</v>
       </c>
       <c r="E44" t="n">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -11037,7 +11037,7 @@
         <v>44993</v>
       </c>
       <c r="E45" t="n">
-        <v>1137</v>
+        <v>1142</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -11063,7 +11063,7 @@
         <v>45145</v>
       </c>
       <c r="E46" t="n">
-        <v>985</v>
+        <v>990</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -11089,7 +11089,7 @@
         <v>45147</v>
       </c>
       <c r="E47" t="n">
-        <v>983</v>
+        <v>988</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -11115,7 +11115,7 @@
         <v>45150</v>
       </c>
       <c r="E48" t="n">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -11141,7 +11141,7 @@
         <v>45205</v>
       </c>
       <c r="E49" t="n">
-        <v>925</v>
+        <v>930</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -11167,7 +11167,7 @@
         <v>45239</v>
       </c>
       <c r="E50" t="n">
-        <v>891</v>
+        <v>896</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -11193,7 +11193,7 @@
         <v>45240</v>
       </c>
       <c r="E51" t="n">
-        <v>890</v>
+        <v>895</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -11219,7 +11219,7 @@
         <v>45264</v>
       </c>
       <c r="E52" t="n">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -11245,7 +11245,7 @@
         <v>45324</v>
       </c>
       <c r="E53" t="n">
-        <v>806</v>
+        <v>811</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -11271,7 +11271,7 @@
         <v>45328</v>
       </c>
       <c r="E54" t="n">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -11297,7 +11297,7 @@
         <v>45333</v>
       </c>
       <c r="E55" t="n">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -11323,7 +11323,7 @@
         <v>45356</v>
       </c>
       <c r="E56" t="n">
-        <v>774</v>
+        <v>779</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -11349,7 +11349,7 @@
         <v>45386</v>
       </c>
       <c r="E57" t="n">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -11375,7 +11375,7 @@
         <v>45390</v>
       </c>
       <c r="E58" t="n">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -11401,7 +11401,7 @@
         <v>45390</v>
       </c>
       <c r="E59" t="n">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -11427,7 +11427,7 @@
         <v>45394</v>
       </c>
       <c r="E60" t="n">
-        <v>736</v>
+        <v>741</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -11453,7 +11453,7 @@
         <v>45414</v>
       </c>
       <c r="E61" t="n">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -11479,7 +11479,7 @@
         <v>45419</v>
       </c>
       <c r="E62" t="n">
-        <v>711</v>
+        <v>716</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -11505,7 +11505,7 @@
         <v>45449</v>
       </c>
       <c r="E63" t="n">
-        <v>681</v>
+        <v>686</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -11531,7 +11531,7 @@
         <v>45474</v>
       </c>
       <c r="E64" t="n">
-        <v>656</v>
+        <v>661</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -11557,7 +11557,7 @@
         <v>45476</v>
       </c>
       <c r="E65" t="n">
-        <v>654</v>
+        <v>659</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -11583,7 +11583,7 @@
         <v>45483</v>
       </c>
       <c r="E66" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -11609,7 +11609,7 @@
         <v>45538</v>
       </c>
       <c r="E67" t="n">
-        <v>592</v>
+        <v>597</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -11635,7 +11635,7 @@
         <v>45544</v>
       </c>
       <c r="E68" t="n">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -11661,7 +11661,7 @@
         <v>45547</v>
       </c>
       <c r="E69" t="n">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -11687,7 +11687,7 @@
         <v>45601</v>
       </c>
       <c r="E70" t="n">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -11713,7 +11713,7 @@
         <v>45607</v>
       </c>
       <c r="E71" t="n">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -11739,7 +11739,7 @@
         <v>45627</v>
       </c>
       <c r="E72" t="n">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -11765,7 +11765,7 @@
         <v>45637</v>
       </c>
       <c r="E73" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -11791,7 +11791,7 @@
         <v>45638</v>
       </c>
       <c r="E74" t="n">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -11817,7 +11817,7 @@
         <v>45658</v>
       </c>
       <c r="E75" t="n">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -11843,7 +11843,7 @@
         <v>45662</v>
       </c>
       <c r="E76" t="n">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -11869,7 +11869,7 @@
         <v>45667</v>
       </c>
       <c r="E77" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -11895,7 +11895,7 @@
         <v>45667</v>
       </c>
       <c r="E78" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -11921,7 +11921,7 @@
         <v>45668</v>
       </c>
       <c r="E79" t="n">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -11947,7 +11947,7 @@
         <v>45727</v>
       </c>
       <c r="E80" t="n">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -11973,7 +11973,7 @@
         <v>45756</v>
       </c>
       <c r="E81" t="n">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -11999,7 +11999,7 @@
         <v>45784</v>
       </c>
       <c r="E82" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F82" t="b">
         <v>0</v>
@@ -12025,7 +12025,7 @@
         <v>45788</v>
       </c>
       <c r="E83" t="n">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -12051,7 +12051,7 @@
         <v>45840</v>
       </c>
       <c r="E84" t="n">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -12077,7 +12077,7 @@
         <v>45843</v>
       </c>
       <c r="E85" t="n">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="F85" t="b">
         <v>0</v>
@@ -12103,7 +12103,7 @@
         <v>45845</v>
       </c>
       <c r="E86" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F86" t="b">
         <v>0</v>
@@ -12129,7 +12129,7 @@
         <v>45847</v>
       </c>
       <c r="E87" t="n">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F87" t="b">
         <v>0</v>
@@ -12155,7 +12155,7 @@
         <v>45873</v>
       </c>
       <c r="E88" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F88" t="b">
         <v>0</v>
@@ -12181,7 +12181,7 @@
         <v>45876</v>
       </c>
       <c r="E89" t="n">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -12207,7 +12207,7 @@
         <v>45907</v>
       </c>
       <c r="E90" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F90" t="b">
         <v>0</v>
@@ -12233,7 +12233,7 @@
         <v>45931</v>
       </c>
       <c r="E91" t="n">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F91" t="b">
         <v>0</v>
@@ -12259,7 +12259,7 @@
         <v>45936</v>
       </c>
       <c r="E92" t="n">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -12285,7 +12285,7 @@
         <v>45938</v>
       </c>
       <c r="E93" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F93" t="b">
         <v>0</v>
@@ -12311,7 +12311,7 @@
         <v>45964</v>
       </c>
       <c r="E94" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="F94" t="b">
         <v>0</v>
@@ -12337,7 +12337,7 @@
         <v>45965</v>
       </c>
       <c r="E95" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F95" t="b">
         <v>0</v>
@@ -12363,7 +12363,7 @@
         <v>45969</v>
       </c>
       <c r="E96" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F96" t="b">
         <v>0</v>
@@ -12389,7 +12389,7 @@
         <v>45997</v>
       </c>
       <c r="E97" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="F97" t="b">
         <v>0</v>
@@ -12415,7 +12415,7 @@
         <v>46060</v>
       </c>
       <c r="E98" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
@@ -12441,7 +12441,7 @@
         <v>46084</v>
       </c>
       <c r="E99" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F99" t="b">
         <v>0</v>
@@ -12467,7 +12467,7 @@
         <v>46090</v>
       </c>
       <c r="E100" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -12493,7 +12493,7 @@
         <v>46114</v>
       </c>
       <c r="E101" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F101" t="b">
         <v>0</v>
@@ -33975,7 +33975,7 @@
         <v>46143</v>
       </c>
       <c r="E996" t="n">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="F996" t="b">
         <v>0</v>
@@ -34001,7 +34001,7 @@
         <v>46204</v>
       </c>
       <c r="E997" t="n">
-        <v>-74</v>
+        <v>-69</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -34027,7 +34027,7 @@
         <v>46236</v>
       </c>
       <c r="E998" t="n">
-        <v>-106</v>
+        <v>-101</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -34053,7 +34053,7 @@
         <v>46238</v>
       </c>
       <c r="E999" t="n">
-        <v>-108</v>
+        <v>-103</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -34079,7 +34079,7 @@
         <v>46270</v>
       </c>
       <c r="E1000" t="n">
-        <v>-140</v>
+        <v>-135</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -34105,7 +34105,7 @@
         <v>46327</v>
       </c>
       <c r="E1001" t="n">
-        <v>-197</v>
+        <v>-192</v>
       </c>
       <c r="F1001" t="b">
         <v>0</v>
@@ -34131,7 +34131,7 @@
         <v>46358</v>
       </c>
       <c r="E1002" t="n">
-        <v>-228</v>
+        <v>-223</v>
       </c>
       <c r="F1002" t="b">
         <v>0</v>
